--- a/data/trans_bre/P19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,77</t>
+          <t>-4,3; 5,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,51</t>
+          <t>1,94; 11,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 7,17</t>
+          <t>-3,68; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,6</t>
+          <t>0,39; 11,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 30,77</t>
+          <t>-17,58; 30,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 58,55</t>
+          <t>7,92; 60,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 28,85</t>
+          <t>-11,89; 29,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 31,87</t>
+          <t>1,11; 29,72</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,44</t>
+          <t>-3,1; 6,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 0,85</t>
+          <t>-7,96; 0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,92</t>
+          <t>-4,03; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 30,51</t>
+          <t>-0,65; 31,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 26,48</t>
+          <t>-10,28; 25,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 3,13</t>
+          <t>-24,83; 2,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 17,5</t>
+          <t>-10,17; 17,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 134,57</t>
+          <t>-1,25; 150,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,82</t>
+          <t>-2,05; 8,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 10,21</t>
+          <t>-0,25; 10,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 13,02</t>
+          <t>0,88; 12,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 33,36</t>
+          <t>-5,71; 33,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 36,26</t>
+          <t>-6,43; 32,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 39,56</t>
+          <t>-0,97; 41,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 43,15</t>
+          <t>2,84; 41,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 83,04</t>
+          <t>-12,66; 78,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,96</t>
+          <t>-7,94; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,48</t>
+          <t>-4,79; 4,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,92</t>
+          <t>-4,09; 5,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 2,6</t>
+          <t>-11,87; 2,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 6,07</t>
+          <t>-21,71; 6,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 13,63</t>
+          <t>-12,72; 13,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 13,92</t>
+          <t>-10,24; 14,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 5,47</t>
+          <t>-23,37; 5,37</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,19</t>
+          <t>-2,11; 2,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,1</t>
+          <t>-0,71; 4,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,01</t>
+          <t>-0,38; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 18,45</t>
+          <t>-0,12; 19,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 11,65</t>
+          <t>-6,98; 10,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 14,36</t>
+          <t>-2,39; 14,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 14,8</t>
+          <t>-1,22; 15,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 48,32</t>
+          <t>-0,21; 50,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,74</t>
+          <t>-4,48; 6,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,62</t>
+          <t>1,26; 11,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 7,4</t>
+          <t>-4,08; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 11,31</t>
+          <t>0,71; 11,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 30,54</t>
+          <t>-18,44; 31,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 60,29</t>
+          <t>4,94; 58,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 29,87</t>
+          <t>-13,09; 27,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 29,72</t>
+          <t>1,41; 29,36</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,54</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,19</t>
+          <t>-3,04; 6,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,64</t>
+          <t>-8,07; 0,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,94</t>
+          <t>-3,71; 6,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 31,74</t>
+          <t>-3,26; 5,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 25,57</t>
+          <t>-10,43; 25,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 2,25</t>
+          <t>-24,94; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 17,19</t>
+          <t>-9,46; 18,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 150,21</t>
+          <t>-6,14; 10,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,35</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>-1,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 8,86</t>
+          <t>-1,92; 8,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 10,81</t>
+          <t>-0,18; 10,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 12,81</t>
+          <t>0,83; 12,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 33,31</t>
+          <t>-5,6; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 32,92</t>
+          <t>-6,23; 32,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 41,6</t>
+          <t>-0,89; 40,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 41,99</t>
+          <t>2,37; 41,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 78,04</t>
+          <t>-11,92; 12,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,81%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 1,97</t>
+          <t>-7,99; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,53</t>
+          <t>-4,53; 4,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,2</t>
+          <t>-4,68; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 2,59</t>
+          <t>-3,67; 4,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 6,61</t>
+          <t>-21,8; 6,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 13,96</t>
+          <t>-11,81; 12,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 14,18</t>
+          <t>-11,14; 14,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 5,37</t>
+          <t>-7,14; 10,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,9</t>
+          <t>-1,9; 3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,14</t>
+          <t>-0,86; 4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,15</t>
+          <t>-0,25; 5,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 19,1</t>
+          <t>-0,95; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 10,64</t>
+          <t>-6,44; 11,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,47</t>
+          <t>-2,69; 14,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 15,31</t>
+          <t>-0,69; 15,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 50,78</t>
+          <t>-1,94; 8,52</t>
         </is>
       </c>
     </row>
